--- a/docentes/Ángel Martínez Gerson Hermenegildo - Estadisticos 20221.xlsx
+++ b/docentes/Ángel Martínez Gerson Hermenegildo - Estadisticos 20221.xlsx
@@ -588,16 +588,19 @@
         <v>35</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -611,16 +614,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -634,16 +640,19 @@
         <v>32</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>32</v>
       </c>
-      <c r="E4">
-        <v>32</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -708,7 +717,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -734,7 +743,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -760,7 +769,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>9.4</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Ángel Martínez Gerson Hermenegildo - Estadisticos 20221.xlsx
+++ b/docentes/Ángel Martínez Gerson Hermenegildo - Estadisticos 20221.xlsx
@@ -717,7 +717,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -743,7 +743,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -769,7 +769,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
